--- a/docs/tender-register-template.xlsx
+++ b/docs/tender-register-template.xlsx
@@ -40,12 +40,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="14"/>
     </font>
@@ -56,6 +50,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -135,20 +135,19 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +157,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -235,6 +234,23 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Resource Planning</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Row 2 is an example. Delete it before sending this back, and put one tender per row from row 2 down.
+Do not type anything below or beside the table: saving as CSV picks up every cell on this sheet, and a stray note becomes a tender.
+See the 'How to fill this in' tab for what each column means.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -700,11 +716,6 @@
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Row 2 is an example. Delete it before sending this back, and put one tender per row from row 2 down. See the 'How to fill this in' tab for what each column means.</t>
-        </is>
-      </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
@@ -3196,6 +3207,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3215,418 +3227,418 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Tender register: what goes in each column</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>One row per tender. Only 'title' has to be filled in; everything else can be left blank and added later in the system. A blank cell never overwrites something already recorded, so this file can be sent back more than once as it gets more complete.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>What the tender is called. Use the wording from the RFQ so it can be found again.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Provision of ERP support and maintenance services</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>reference_number</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>The issuing authority's bid number. Worth filling in: it is how the system recognises a tender it has already seen, so this file can be re-sent without creating duplicates.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>SCM/2026/0148</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>The organisation putting the work out.</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>City of Cape Town</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Where the work happens.</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Cape Town</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Rand value. Digits only, no R and no spaces. Leave blank if not published.</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>12500000</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>submission_deadline</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>When the bid is due. See the date note below.</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>contract_start_date</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>When the work would start if we win it.</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>2027-01-04</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>contract_end_date</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>When it would finish. Leave blank if open ended.</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>2029-12-31</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>One of: draft, live, submitted, won, lost. Pick from the dropdown. Blank is read as draft.</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>seats</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>The people the tender needs. Separate each role with a pipe. Put the number first with an x, and the minimum years after an @. Both are optional: a bare role name means one person with no experience floor.</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>3 x Business Analyst @5 | Project Manager @8 | 2 x ERP Consultant</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>required_skills</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Skills named in the RFQ, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Microsoft Dynamics 365 | SQL | Power BI</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>required_certifications</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Certifications named in the RFQ, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>PMP | ITIL Foundation</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Sectors the work falls under, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Public Sector | Technology</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>min_experience_years</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>A years figure that applies to the whole tender. Any seat with its own @ number overrides it.</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>reference_letters_required</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>How many client reference letters the tender asks for. Put 0 if it genuinely asks for none, and leave blank if nobody has checked the RFQ yet. Those are different things.</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Three things that will cause a row to be rejected</t>
         </is>
       </c>
     </row>
     <row r="22" ht="62" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Dates must read 2026-10-15</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Year, then month, then day. 15/10/2026 is rejected rather than guessed at, because whether it means 15 October or the 10th of a 15th month depends on who saved the file, and guessing wrong puts a contract in the wrong month where nobody notices until it needs extending.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="62" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Role names have to match the ones the system knows</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Write 'Business Analyst', not 'BA' or 'Snr BA'. The system scores a candidate against the exact role on the seat, so an abbreviation it does not recognise scores zero and the tender reports that nobody can fill the seat, even when three people obviously can. Common short forms like BA and PM are expanded automatically, and anything else is reported back to you in a list rather than quietly accepted.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Use a pipe between list items</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Skills, certifications, sectors and seats all separate with a pipe. Commas are fine inside an item, so 'Roads, bridges and structures' stays as one thing.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>When it is filled in: save as CSV (File, Save As, CSV UTF-8) and send that. Nothing is written to the system until the file has been read back to you first.</t>
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>When it is filled in: save as CSV (File, Save As, CSV UTF-8) and send that. It is read with  npx tsx scripts/import-tenders.ts &lt;file.csv&gt;  which prints back exactly what it would do and writes nothing. Only a second run with --apply writes.</t>
         </is>
       </c>
     </row>

--- a/docs/tender-register-template.xlsx
+++ b/docs/tender-register-template.xlsx
@@ -542,24 +542,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O500"/>
+  <dimension ref="A1:P500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="56" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -570,70 +571,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>reference_number</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>client</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>submission_deadline</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>contract_start_date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>contract_end_date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>seats</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>required_skills</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>required_certifications</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>min_experience_years</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>reference_letters_required</t>
         </is>
@@ -647,2563 +653,2571 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Tipp Consulting</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>SCM/2026/0148</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>City of Cape Town</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Cape Town</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>12500000</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>2027-01-04</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>2029-12-31</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>3 x Business Analyst @5 | Project Manager @8 | 2 x ERP Consultant</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Microsoft Dynamics 365 | SQL | Power BI</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>PMP</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Public Sector | Technology</t>
         </is>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="P2" s="2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
-      <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
       <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="F43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="F44" s="5" t="n"/>
       <c r="G44" s="5" t="n"/>
       <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="F46" s="5" t="n"/>
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="F47" s="5" t="n"/>
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="F48" s="5" t="n"/>
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
     </row>
     <row r="49">
-      <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
     </row>
     <row r="50">
-      <c r="F50" s="5" t="n"/>
       <c r="G50" s="5" t="n"/>
       <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
     </row>
     <row r="51">
-      <c r="F51" s="5" t="n"/>
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="F52" s="5" t="n"/>
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
     </row>
     <row r="53">
-      <c r="F53" s="5" t="n"/>
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
     </row>
     <row r="55">
-      <c r="F55" s="5" t="n"/>
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="F56" s="5" t="n"/>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="F57" s="5" t="n"/>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
     </row>
     <row r="58">
-      <c r="F58" s="5" t="n"/>
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="F59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="F60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
       <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="F61" s="5" t="n"/>
       <c r="G61" s="5" t="n"/>
       <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="F62" s="5" t="n"/>
       <c r="G62" s="5" t="n"/>
       <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
     </row>
     <row r="63">
-      <c r="F63" s="5" t="n"/>
       <c r="G63" s="5" t="n"/>
       <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="F64" s="5" t="n"/>
       <c r="G64" s="5" t="n"/>
       <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="F65" s="5" t="n"/>
       <c r="G65" s="5" t="n"/>
       <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="F66" s="5" t="n"/>
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
     </row>
     <row r="67">
-      <c r="F67" s="5" t="n"/>
       <c r="G67" s="5" t="n"/>
       <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="F68" s="5" t="n"/>
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="5" t="n"/>
+      <c r="I68" s="5" t="n"/>
     </row>
     <row r="69">
-      <c r="F69" s="5" t="n"/>
       <c r="G69" s="5" t="n"/>
       <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="F70" s="5" t="n"/>
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="F71" s="5" t="n"/>
       <c r="G71" s="5" t="n"/>
       <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="F72" s="5" t="n"/>
       <c r="G72" s="5" t="n"/>
       <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="F73" s="5" t="n"/>
       <c r="G73" s="5" t="n"/>
       <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
     </row>
     <row r="74">
-      <c r="F74" s="5" t="n"/>
       <c r="G74" s="5" t="n"/>
       <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="F75" s="5" t="n"/>
       <c r="G75" s="5" t="n"/>
       <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
     </row>
     <row r="76">
-      <c r="F76" s="5" t="n"/>
       <c r="G76" s="5" t="n"/>
       <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="F77" s="5" t="n"/>
       <c r="G77" s="5" t="n"/>
       <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="F78" s="5" t="n"/>
       <c r="G78" s="5" t="n"/>
       <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
     </row>
     <row r="79">
-      <c r="F79" s="5" t="n"/>
       <c r="G79" s="5" t="n"/>
       <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="F80" s="5" t="n"/>
       <c r="G80" s="5" t="n"/>
       <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="F81" s="5" t="n"/>
       <c r="G81" s="5" t="n"/>
       <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="F82" s="5" t="n"/>
       <c r="G82" s="5" t="n"/>
       <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="n"/>
     </row>
     <row r="83">
-      <c r="F83" s="5" t="n"/>
       <c r="G83" s="5" t="n"/>
       <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="F84" s="5" t="n"/>
       <c r="G84" s="5" t="n"/>
       <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n"/>
     </row>
     <row r="85">
-      <c r="F85" s="5" t="n"/>
       <c r="G85" s="5" t="n"/>
       <c r="H85" s="5" t="n"/>
+      <c r="I85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="F86" s="5" t="n"/>
       <c r="G86" s="5" t="n"/>
       <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="F87" s="5" t="n"/>
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
     </row>
     <row r="88">
-      <c r="F88" s="5" t="n"/>
       <c r="G88" s="5" t="n"/>
       <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="F89" s="5" t="n"/>
       <c r="G89" s="5" t="n"/>
       <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
     </row>
     <row r="90">
-      <c r="F90" s="5" t="n"/>
       <c r="G90" s="5" t="n"/>
       <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
     </row>
     <row r="91">
-      <c r="F91" s="5" t="n"/>
       <c r="G91" s="5" t="n"/>
       <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="F92" s="5" t="n"/>
       <c r="G92" s="5" t="n"/>
       <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
     </row>
     <row r="93">
-      <c r="F93" s="5" t="n"/>
       <c r="G93" s="5" t="n"/>
       <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="F94" s="5" t="n"/>
       <c r="G94" s="5" t="n"/>
       <c r="H94" s="5" t="n"/>
+      <c r="I94" s="5" t="n"/>
     </row>
     <row r="95">
-      <c r="F95" s="5" t="n"/>
       <c r="G95" s="5" t="n"/>
       <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="F96" s="5" t="n"/>
       <c r="G96" s="5" t="n"/>
       <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
     </row>
     <row r="97">
-      <c r="F97" s="5" t="n"/>
       <c r="G97" s="5" t="n"/>
       <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="F98" s="5" t="n"/>
       <c r="G98" s="5" t="n"/>
       <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
     </row>
     <row r="99">
-      <c r="F99" s="5" t="n"/>
       <c r="G99" s="5" t="n"/>
       <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="n"/>
     </row>
     <row r="100">
-      <c r="F100" s="5" t="n"/>
       <c r="G100" s="5" t="n"/>
       <c r="H100" s="5" t="n"/>
+      <c r="I100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="F101" s="5" t="n"/>
       <c r="G101" s="5" t="n"/>
       <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n"/>
     </row>
     <row r="102">
-      <c r="F102" s="5" t="n"/>
       <c r="G102" s="5" t="n"/>
       <c r="H102" s="5" t="n"/>
+      <c r="I102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="F103" s="5" t="n"/>
       <c r="G103" s="5" t="n"/>
       <c r="H103" s="5" t="n"/>
+      <c r="I103" s="5" t="n"/>
     </row>
     <row r="104">
-      <c r="F104" s="5" t="n"/>
       <c r="G104" s="5" t="n"/>
       <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="F105" s="5" t="n"/>
       <c r="G105" s="5" t="n"/>
       <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
     </row>
     <row r="106">
-      <c r="F106" s="5" t="n"/>
       <c r="G106" s="5" t="n"/>
       <c r="H106" s="5" t="n"/>
+      <c r="I106" s="5" t="n"/>
     </row>
     <row r="107">
-      <c r="F107" s="5" t="n"/>
       <c r="G107" s="5" t="n"/>
       <c r="H107" s="5" t="n"/>
+      <c r="I107" s="5" t="n"/>
     </row>
     <row r="108">
-      <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="n"/>
       <c r="H108" s="5" t="n"/>
+      <c r="I108" s="5" t="n"/>
     </row>
     <row r="109">
-      <c r="F109" s="5" t="n"/>
       <c r="G109" s="5" t="n"/>
       <c r="H109" s="5" t="n"/>
+      <c r="I109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="F110" s="5" t="n"/>
       <c r="G110" s="5" t="n"/>
       <c r="H110" s="5" t="n"/>
+      <c r="I110" s="5" t="n"/>
     </row>
     <row r="111">
-      <c r="F111" s="5" t="n"/>
       <c r="G111" s="5" t="n"/>
       <c r="H111" s="5" t="n"/>
+      <c r="I111" s="5" t="n"/>
     </row>
     <row r="112">
-      <c r="F112" s="5" t="n"/>
       <c r="G112" s="5" t="n"/>
       <c r="H112" s="5" t="n"/>
+      <c r="I112" s="5" t="n"/>
     </row>
     <row r="113">
-      <c r="F113" s="5" t="n"/>
       <c r="G113" s="5" t="n"/>
       <c r="H113" s="5" t="n"/>
+      <c r="I113" s="5" t="n"/>
     </row>
     <row r="114">
-      <c r="F114" s="5" t="n"/>
       <c r="G114" s="5" t="n"/>
       <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n"/>
     </row>
     <row r="115">
-      <c r="F115" s="5" t="n"/>
       <c r="G115" s="5" t="n"/>
       <c r="H115" s="5" t="n"/>
+      <c r="I115" s="5" t="n"/>
     </row>
     <row r="116">
-      <c r="F116" s="5" t="n"/>
       <c r="G116" s="5" t="n"/>
       <c r="H116" s="5" t="n"/>
+      <c r="I116" s="5" t="n"/>
     </row>
     <row r="117">
-      <c r="F117" s="5" t="n"/>
       <c r="G117" s="5" t="n"/>
       <c r="H117" s="5" t="n"/>
+      <c r="I117" s="5" t="n"/>
     </row>
     <row r="118">
-      <c r="F118" s="5" t="n"/>
       <c r="G118" s="5" t="n"/>
       <c r="H118" s="5" t="n"/>
+      <c r="I118" s="5" t="n"/>
     </row>
     <row r="119">
-      <c r="F119" s="5" t="n"/>
       <c r="G119" s="5" t="n"/>
       <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
     </row>
     <row r="120">
-      <c r="F120" s="5" t="n"/>
       <c r="G120" s="5" t="n"/>
       <c r="H120" s="5" t="n"/>
+      <c r="I120" s="5" t="n"/>
     </row>
     <row r="121">
-      <c r="F121" s="5" t="n"/>
       <c r="G121" s="5" t="n"/>
       <c r="H121" s="5" t="n"/>
+      <c r="I121" s="5" t="n"/>
     </row>
     <row r="122">
-      <c r="F122" s="5" t="n"/>
       <c r="G122" s="5" t="n"/>
       <c r="H122" s="5" t="n"/>
+      <c r="I122" s="5" t="n"/>
     </row>
     <row r="123">
-      <c r="F123" s="5" t="n"/>
       <c r="G123" s="5" t="n"/>
       <c r="H123" s="5" t="n"/>
+      <c r="I123" s="5" t="n"/>
     </row>
     <row r="124">
-      <c r="F124" s="5" t="n"/>
       <c r="G124" s="5" t="n"/>
       <c r="H124" s="5" t="n"/>
+      <c r="I124" s="5" t="n"/>
     </row>
     <row r="125">
-      <c r="F125" s="5" t="n"/>
       <c r="G125" s="5" t="n"/>
       <c r="H125" s="5" t="n"/>
+      <c r="I125" s="5" t="n"/>
     </row>
     <row r="126">
-      <c r="F126" s="5" t="n"/>
       <c r="G126" s="5" t="n"/>
       <c r="H126" s="5" t="n"/>
+      <c r="I126" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="F127" s="5" t="n"/>
       <c r="G127" s="5" t="n"/>
       <c r="H127" s="5" t="n"/>
+      <c r="I127" s="5" t="n"/>
     </row>
     <row r="128">
-      <c r="F128" s="5" t="n"/>
       <c r="G128" s="5" t="n"/>
       <c r="H128" s="5" t="n"/>
+      <c r="I128" s="5" t="n"/>
     </row>
     <row r="129">
-      <c r="F129" s="5" t="n"/>
       <c r="G129" s="5" t="n"/>
       <c r="H129" s="5" t="n"/>
+      <c r="I129" s="5" t="n"/>
     </row>
     <row r="130">
-      <c r="F130" s="5" t="n"/>
       <c r="G130" s="5" t="n"/>
       <c r="H130" s="5" t="n"/>
+      <c r="I130" s="5" t="n"/>
     </row>
     <row r="131">
-      <c r="F131" s="5" t="n"/>
       <c r="G131" s="5" t="n"/>
       <c r="H131" s="5" t="n"/>
+      <c r="I131" s="5" t="n"/>
     </row>
     <row r="132">
-      <c r="F132" s="5" t="n"/>
       <c r="G132" s="5" t="n"/>
       <c r="H132" s="5" t="n"/>
+      <c r="I132" s="5" t="n"/>
     </row>
     <row r="133">
-      <c r="F133" s="5" t="n"/>
       <c r="G133" s="5" t="n"/>
       <c r="H133" s="5" t="n"/>
+      <c r="I133" s="5" t="n"/>
     </row>
     <row r="134">
-      <c r="F134" s="5" t="n"/>
       <c r="G134" s="5" t="n"/>
       <c r="H134" s="5" t="n"/>
+      <c r="I134" s="5" t="n"/>
     </row>
     <row r="135">
-      <c r="F135" s="5" t="n"/>
       <c r="G135" s="5" t="n"/>
       <c r="H135" s="5" t="n"/>
+      <c r="I135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="F136" s="5" t="n"/>
       <c r="G136" s="5" t="n"/>
       <c r="H136" s="5" t="n"/>
+      <c r="I136" s="5" t="n"/>
     </row>
     <row r="137">
-      <c r="F137" s="5" t="n"/>
       <c r="G137" s="5" t="n"/>
       <c r="H137" s="5" t="n"/>
+      <c r="I137" s="5" t="n"/>
     </row>
     <row r="138">
-      <c r="F138" s="5" t="n"/>
       <c r="G138" s="5" t="n"/>
       <c r="H138" s="5" t="n"/>
+      <c r="I138" s="5" t="n"/>
     </row>
     <row r="139">
-      <c r="F139" s="5" t="n"/>
       <c r="G139" s="5" t="n"/>
       <c r="H139" s="5" t="n"/>
+      <c r="I139" s="5" t="n"/>
     </row>
     <row r="140">
-      <c r="F140" s="5" t="n"/>
       <c r="G140" s="5" t="n"/>
       <c r="H140" s="5" t="n"/>
+      <c r="I140" s="5" t="n"/>
     </row>
     <row r="141">
-      <c r="F141" s="5" t="n"/>
       <c r="G141" s="5" t="n"/>
       <c r="H141" s="5" t="n"/>
+      <c r="I141" s="5" t="n"/>
     </row>
     <row r="142">
-      <c r="F142" s="5" t="n"/>
       <c r="G142" s="5" t="n"/>
       <c r="H142" s="5" t="n"/>
+      <c r="I142" s="5" t="n"/>
     </row>
     <row r="143">
-      <c r="F143" s="5" t="n"/>
       <c r="G143" s="5" t="n"/>
       <c r="H143" s="5" t="n"/>
+      <c r="I143" s="5" t="n"/>
     </row>
     <row r="144">
-      <c r="F144" s="5" t="n"/>
       <c r="G144" s="5" t="n"/>
       <c r="H144" s="5" t="n"/>
+      <c r="I144" s="5" t="n"/>
     </row>
     <row r="145">
-      <c r="F145" s="5" t="n"/>
       <c r="G145" s="5" t="n"/>
       <c r="H145" s="5" t="n"/>
+      <c r="I145" s="5" t="n"/>
     </row>
     <row r="146">
-      <c r="F146" s="5" t="n"/>
       <c r="G146" s="5" t="n"/>
       <c r="H146" s="5" t="n"/>
+      <c r="I146" s="5" t="n"/>
     </row>
     <row r="147">
-      <c r="F147" s="5" t="n"/>
       <c r="G147" s="5" t="n"/>
       <c r="H147" s="5" t="n"/>
+      <c r="I147" s="5" t="n"/>
     </row>
     <row r="148">
-      <c r="F148" s="5" t="n"/>
       <c r="G148" s="5" t="n"/>
       <c r="H148" s="5" t="n"/>
+      <c r="I148" s="5" t="n"/>
     </row>
     <row r="149">
-      <c r="F149" s="5" t="n"/>
       <c r="G149" s="5" t="n"/>
       <c r="H149" s="5" t="n"/>
+      <c r="I149" s="5" t="n"/>
     </row>
     <row r="150">
-      <c r="F150" s="5" t="n"/>
       <c r="G150" s="5" t="n"/>
       <c r="H150" s="5" t="n"/>
+      <c r="I150" s="5" t="n"/>
     </row>
     <row r="151">
-      <c r="F151" s="5" t="n"/>
       <c r="G151" s="5" t="n"/>
       <c r="H151" s="5" t="n"/>
+      <c r="I151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="F152" s="5" t="n"/>
       <c r="G152" s="5" t="n"/>
       <c r="H152" s="5" t="n"/>
+      <c r="I152" s="5" t="n"/>
     </row>
     <row r="153">
-      <c r="F153" s="5" t="n"/>
       <c r="G153" s="5" t="n"/>
       <c r="H153" s="5" t="n"/>
+      <c r="I153" s="5" t="n"/>
     </row>
     <row r="154">
-      <c r="F154" s="5" t="n"/>
       <c r="G154" s="5" t="n"/>
       <c r="H154" s="5" t="n"/>
+      <c r="I154" s="5" t="n"/>
     </row>
     <row r="155">
-      <c r="F155" s="5" t="n"/>
       <c r="G155" s="5" t="n"/>
       <c r="H155" s="5" t="n"/>
+      <c r="I155" s="5" t="n"/>
     </row>
     <row r="156">
-      <c r="F156" s="5" t="n"/>
       <c r="G156" s="5" t="n"/>
       <c r="H156" s="5" t="n"/>
+      <c r="I156" s="5" t="n"/>
     </row>
     <row r="157">
-      <c r="F157" s="5" t="n"/>
       <c r="G157" s="5" t="n"/>
       <c r="H157" s="5" t="n"/>
+      <c r="I157" s="5" t="n"/>
     </row>
     <row r="158">
-      <c r="F158" s="5" t="n"/>
       <c r="G158" s="5" t="n"/>
       <c r="H158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="F159" s="5" t="n"/>
       <c r="G159" s="5" t="n"/>
       <c r="H159" s="5" t="n"/>
+      <c r="I159" s="5" t="n"/>
     </row>
     <row r="160">
-      <c r="F160" s="5" t="n"/>
       <c r="G160" s="5" t="n"/>
       <c r="H160" s="5" t="n"/>
+      <c r="I160" s="5" t="n"/>
     </row>
     <row r="161">
-      <c r="F161" s="5" t="n"/>
       <c r="G161" s="5" t="n"/>
       <c r="H161" s="5" t="n"/>
+      <c r="I161" s="5" t="n"/>
     </row>
     <row r="162">
-      <c r="F162" s="5" t="n"/>
       <c r="G162" s="5" t="n"/>
       <c r="H162" s="5" t="n"/>
+      <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="F163" s="5" t="n"/>
       <c r="G163" s="5" t="n"/>
       <c r="H163" s="5" t="n"/>
+      <c r="I163" s="5" t="n"/>
     </row>
     <row r="164">
-      <c r="F164" s="5" t="n"/>
       <c r="G164" s="5" t="n"/>
       <c r="H164" s="5" t="n"/>
+      <c r="I164" s="5" t="n"/>
     </row>
     <row r="165">
-      <c r="F165" s="5" t="n"/>
       <c r="G165" s="5" t="n"/>
       <c r="H165" s="5" t="n"/>
+      <c r="I165" s="5" t="n"/>
     </row>
     <row r="166">
-      <c r="F166" s="5" t="n"/>
       <c r="G166" s="5" t="n"/>
       <c r="H166" s="5" t="n"/>
+      <c r="I166" s="5" t="n"/>
     </row>
     <row r="167">
-      <c r="F167" s="5" t="n"/>
       <c r="G167" s="5" t="n"/>
       <c r="H167" s="5" t="n"/>
+      <c r="I167" s="5" t="n"/>
     </row>
     <row r="168">
-      <c r="F168" s="5" t="n"/>
       <c r="G168" s="5" t="n"/>
       <c r="H168" s="5" t="n"/>
+      <c r="I168" s="5" t="n"/>
     </row>
     <row r="169">
-      <c r="F169" s="5" t="n"/>
       <c r="G169" s="5" t="n"/>
       <c r="H169" s="5" t="n"/>
+      <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
-      <c r="F170" s="5" t="n"/>
       <c r="G170" s="5" t="n"/>
       <c r="H170" s="5" t="n"/>
+      <c r="I170" s="5" t="n"/>
     </row>
     <row r="171">
-      <c r="F171" s="5" t="n"/>
       <c r="G171" s="5" t="n"/>
       <c r="H171" s="5" t="n"/>
+      <c r="I171" s="5" t="n"/>
     </row>
     <row r="172">
-      <c r="F172" s="5" t="n"/>
       <c r="G172" s="5" t="n"/>
       <c r="H172" s="5" t="n"/>
+      <c r="I172" s="5" t="n"/>
     </row>
     <row r="173">
-      <c r="F173" s="5" t="n"/>
       <c r="G173" s="5" t="n"/>
       <c r="H173" s="5" t="n"/>
+      <c r="I173" s="5" t="n"/>
     </row>
     <row r="174">
-      <c r="F174" s="5" t="n"/>
       <c r="G174" s="5" t="n"/>
       <c r="H174" s="5" t="n"/>
+      <c r="I174" s="5" t="n"/>
     </row>
     <row r="175">
-      <c r="F175" s="5" t="n"/>
       <c r="G175" s="5" t="n"/>
       <c r="H175" s="5" t="n"/>
+      <c r="I175" s="5" t="n"/>
     </row>
     <row r="176">
-      <c r="F176" s="5" t="n"/>
       <c r="G176" s="5" t="n"/>
       <c r="H176" s="5" t="n"/>
+      <c r="I176" s="5" t="n"/>
     </row>
     <row r="177">
-      <c r="F177" s="5" t="n"/>
       <c r="G177" s="5" t="n"/>
       <c r="H177" s="5" t="n"/>
+      <c r="I177" s="5" t="n"/>
     </row>
     <row r="178">
-      <c r="F178" s="5" t="n"/>
       <c r="G178" s="5" t="n"/>
       <c r="H178" s="5" t="n"/>
+      <c r="I178" s="5" t="n"/>
     </row>
     <row r="179">
-      <c r="F179" s="5" t="n"/>
       <c r="G179" s="5" t="n"/>
       <c r="H179" s="5" t="n"/>
+      <c r="I179" s="5" t="n"/>
     </row>
     <row r="180">
-      <c r="F180" s="5" t="n"/>
       <c r="G180" s="5" t="n"/>
       <c r="H180" s="5" t="n"/>
+      <c r="I180" s="5" t="n"/>
     </row>
     <row r="181">
-      <c r="F181" s="5" t="n"/>
       <c r="G181" s="5" t="n"/>
       <c r="H181" s="5" t="n"/>
+      <c r="I181" s="5" t="n"/>
     </row>
     <row r="182">
-      <c r="F182" s="5" t="n"/>
       <c r="G182" s="5" t="n"/>
       <c r="H182" s="5" t="n"/>
+      <c r="I182" s="5" t="n"/>
     </row>
     <row r="183">
-      <c r="F183" s="5" t="n"/>
       <c r="G183" s="5" t="n"/>
       <c r="H183" s="5" t="n"/>
+      <c r="I183" s="5" t="n"/>
     </row>
     <row r="184">
-      <c r="F184" s="5" t="n"/>
       <c r="G184" s="5" t="n"/>
       <c r="H184" s="5" t="n"/>
+      <c r="I184" s="5" t="n"/>
     </row>
     <row r="185">
-      <c r="F185" s="5" t="n"/>
       <c r="G185" s="5" t="n"/>
       <c r="H185" s="5" t="n"/>
+      <c r="I185" s="5" t="n"/>
     </row>
     <row r="186">
-      <c r="F186" s="5" t="n"/>
       <c r="G186" s="5" t="n"/>
       <c r="H186" s="5" t="n"/>
+      <c r="I186" s="5" t="n"/>
     </row>
     <row r="187">
-      <c r="F187" s="5" t="n"/>
       <c r="G187" s="5" t="n"/>
       <c r="H187" s="5" t="n"/>
+      <c r="I187" s="5" t="n"/>
     </row>
     <row r="188">
-      <c r="F188" s="5" t="n"/>
       <c r="G188" s="5" t="n"/>
       <c r="H188" s="5" t="n"/>
+      <c r="I188" s="5" t="n"/>
     </row>
     <row r="189">
-      <c r="F189" s="5" t="n"/>
       <c r="G189" s="5" t="n"/>
       <c r="H189" s="5" t="n"/>
+      <c r="I189" s="5" t="n"/>
     </row>
     <row r="190">
-      <c r="F190" s="5" t="n"/>
       <c r="G190" s="5" t="n"/>
       <c r="H190" s="5" t="n"/>
+      <c r="I190" s="5" t="n"/>
     </row>
     <row r="191">
-      <c r="F191" s="5" t="n"/>
       <c r="G191" s="5" t="n"/>
       <c r="H191" s="5" t="n"/>
+      <c r="I191" s="5" t="n"/>
     </row>
     <row r="192">
-      <c r="F192" s="5" t="n"/>
       <c r="G192" s="5" t="n"/>
       <c r="H192" s="5" t="n"/>
+      <c r="I192" s="5" t="n"/>
     </row>
     <row r="193">
-      <c r="F193" s="5" t="n"/>
       <c r="G193" s="5" t="n"/>
       <c r="H193" s="5" t="n"/>
+      <c r="I193" s="5" t="n"/>
     </row>
     <row r="194">
-      <c r="F194" s="5" t="n"/>
       <c r="G194" s="5" t="n"/>
       <c r="H194" s="5" t="n"/>
+      <c r="I194" s="5" t="n"/>
     </row>
     <row r="195">
-      <c r="F195" s="5" t="n"/>
       <c r="G195" s="5" t="n"/>
       <c r="H195" s="5" t="n"/>
+      <c r="I195" s="5" t="n"/>
     </row>
     <row r="196">
-      <c r="F196" s="5" t="n"/>
       <c r="G196" s="5" t="n"/>
       <c r="H196" s="5" t="n"/>
+      <c r="I196" s="5" t="n"/>
     </row>
     <row r="197">
-      <c r="F197" s="5" t="n"/>
       <c r="G197" s="5" t="n"/>
       <c r="H197" s="5" t="n"/>
+      <c r="I197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="F198" s="5" t="n"/>
       <c r="G198" s="5" t="n"/>
       <c r="H198" s="5" t="n"/>
+      <c r="I198" s="5" t="n"/>
     </row>
     <row r="199">
-      <c r="F199" s="5" t="n"/>
       <c r="G199" s="5" t="n"/>
       <c r="H199" s="5" t="n"/>
+      <c r="I199" s="5" t="n"/>
     </row>
     <row r="200">
-      <c r="F200" s="5" t="n"/>
       <c r="G200" s="5" t="n"/>
       <c r="H200" s="5" t="n"/>
+      <c r="I200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="F201" s="5" t="n"/>
       <c r="G201" s="5" t="n"/>
       <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
     </row>
     <row r="202">
-      <c r="F202" s="5" t="n"/>
       <c r="G202" s="5" t="n"/>
       <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
     </row>
     <row r="203">
-      <c r="F203" s="5" t="n"/>
       <c r="G203" s="5" t="n"/>
       <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
     </row>
     <row r="204">
-      <c r="F204" s="5" t="n"/>
       <c r="G204" s="5" t="n"/>
       <c r="H204" s="5" t="n"/>
+      <c r="I204" s="5" t="n"/>
     </row>
     <row r="205">
-      <c r="F205" s="5" t="n"/>
       <c r="G205" s="5" t="n"/>
       <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
     </row>
     <row r="206">
-      <c r="F206" s="5" t="n"/>
       <c r="G206" s="5" t="n"/>
       <c r="H206" s="5" t="n"/>
+      <c r="I206" s="5" t="n"/>
     </row>
     <row r="207">
-      <c r="F207" s="5" t="n"/>
       <c r="G207" s="5" t="n"/>
       <c r="H207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
     </row>
     <row r="208">
-      <c r="F208" s="5" t="n"/>
       <c r="G208" s="5" t="n"/>
       <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="F209" s="5" t="n"/>
       <c r="G209" s="5" t="n"/>
       <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
     </row>
     <row r="210">
-      <c r="F210" s="5" t="n"/>
       <c r="G210" s="5" t="n"/>
       <c r="H210" s="5" t="n"/>
+      <c r="I210" s="5" t="n"/>
     </row>
     <row r="211">
-      <c r="F211" s="5" t="n"/>
       <c r="G211" s="5" t="n"/>
       <c r="H211" s="5" t="n"/>
+      <c r="I211" s="5" t="n"/>
     </row>
     <row r="212">
-      <c r="F212" s="5" t="n"/>
       <c r="G212" s="5" t="n"/>
       <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
     </row>
     <row r="213">
-      <c r="F213" s="5" t="n"/>
       <c r="G213" s="5" t="n"/>
       <c r="H213" s="5" t="n"/>
+      <c r="I213" s="5" t="n"/>
     </row>
     <row r="214">
-      <c r="F214" s="5" t="n"/>
       <c r="G214" s="5" t="n"/>
       <c r="H214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
     </row>
     <row r="215">
-      <c r="F215" s="5" t="n"/>
       <c r="G215" s="5" t="n"/>
       <c r="H215" s="5" t="n"/>
+      <c r="I215" s="5" t="n"/>
     </row>
     <row r="216">
-      <c r="F216" s="5" t="n"/>
       <c r="G216" s="5" t="n"/>
       <c r="H216" s="5" t="n"/>
+      <c r="I216" s="5" t="n"/>
     </row>
     <row r="217">
-      <c r="F217" s="5" t="n"/>
       <c r="G217" s="5" t="n"/>
       <c r="H217" s="5" t="n"/>
+      <c r="I217" s="5" t="n"/>
     </row>
     <row r="218">
-      <c r="F218" s="5" t="n"/>
       <c r="G218" s="5" t="n"/>
       <c r="H218" s="5" t="n"/>
+      <c r="I218" s="5" t="n"/>
     </row>
     <row r="219">
-      <c r="F219" s="5" t="n"/>
       <c r="G219" s="5" t="n"/>
       <c r="H219" s="5" t="n"/>
+      <c r="I219" s="5" t="n"/>
     </row>
     <row r="220">
-      <c r="F220" s="5" t="n"/>
       <c r="G220" s="5" t="n"/>
       <c r="H220" s="5" t="n"/>
+      <c r="I220" s="5" t="n"/>
     </row>
     <row r="221">
-      <c r="F221" s="5" t="n"/>
       <c r="G221" s="5" t="n"/>
       <c r="H221" s="5" t="n"/>
+      <c r="I221" s="5" t="n"/>
     </row>
     <row r="222">
-      <c r="F222" s="5" t="n"/>
       <c r="G222" s="5" t="n"/>
       <c r="H222" s="5" t="n"/>
+      <c r="I222" s="5" t="n"/>
     </row>
     <row r="223">
-      <c r="F223" s="5" t="n"/>
       <c r="G223" s="5" t="n"/>
       <c r="H223" s="5" t="n"/>
+      <c r="I223" s="5" t="n"/>
     </row>
     <row r="224">
-      <c r="F224" s="5" t="n"/>
       <c r="G224" s="5" t="n"/>
       <c r="H224" s="5" t="n"/>
+      <c r="I224" s="5" t="n"/>
     </row>
     <row r="225">
-      <c r="F225" s="5" t="n"/>
       <c r="G225" s="5" t="n"/>
       <c r="H225" s="5" t="n"/>
+      <c r="I225" s="5" t="n"/>
     </row>
     <row r="226">
-      <c r="F226" s="5" t="n"/>
       <c r="G226" s="5" t="n"/>
       <c r="H226" s="5" t="n"/>
+      <c r="I226" s="5" t="n"/>
     </row>
     <row r="227">
-      <c r="F227" s="5" t="n"/>
       <c r="G227" s="5" t="n"/>
       <c r="H227" s="5" t="n"/>
+      <c r="I227" s="5" t="n"/>
     </row>
     <row r="228">
-      <c r="F228" s="5" t="n"/>
       <c r="G228" s="5" t="n"/>
       <c r="H228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
     </row>
     <row r="229">
-      <c r="F229" s="5" t="n"/>
       <c r="G229" s="5" t="n"/>
       <c r="H229" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
     </row>
     <row r="230">
-      <c r="F230" s="5" t="n"/>
       <c r="G230" s="5" t="n"/>
       <c r="H230" s="5" t="n"/>
+      <c r="I230" s="5" t="n"/>
     </row>
     <row r="231">
-      <c r="F231" s="5" t="n"/>
       <c r="G231" s="5" t="n"/>
       <c r="H231" s="5" t="n"/>
+      <c r="I231" s="5" t="n"/>
     </row>
     <row r="232">
-      <c r="F232" s="5" t="n"/>
       <c r="G232" s="5" t="n"/>
       <c r="H232" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
     </row>
     <row r="233">
-      <c r="F233" s="5" t="n"/>
       <c r="G233" s="5" t="n"/>
       <c r="H233" s="5" t="n"/>
+      <c r="I233" s="5" t="n"/>
     </row>
     <row r="234">
-      <c r="F234" s="5" t="n"/>
       <c r="G234" s="5" t="n"/>
       <c r="H234" s="5" t="n"/>
+      <c r="I234" s="5" t="n"/>
     </row>
     <row r="235">
-      <c r="F235" s="5" t="n"/>
       <c r="G235" s="5" t="n"/>
       <c r="H235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
     </row>
     <row r="236">
-      <c r="F236" s="5" t="n"/>
       <c r="G236" s="5" t="n"/>
       <c r="H236" s="5" t="n"/>
+      <c r="I236" s="5" t="n"/>
     </row>
     <row r="237">
-      <c r="F237" s="5" t="n"/>
       <c r="G237" s="5" t="n"/>
       <c r="H237" s="5" t="n"/>
+      <c r="I237" s="5" t="n"/>
     </row>
     <row r="238">
-      <c r="F238" s="5" t="n"/>
       <c r="G238" s="5" t="n"/>
       <c r="H238" s="5" t="n"/>
+      <c r="I238" s="5" t="n"/>
     </row>
     <row r="239">
-      <c r="F239" s="5" t="n"/>
       <c r="G239" s="5" t="n"/>
       <c r="H239" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
     </row>
     <row r="240">
-      <c r="F240" s="5" t="n"/>
       <c r="G240" s="5" t="n"/>
       <c r="H240" s="5" t="n"/>
+      <c r="I240" s="5" t="n"/>
     </row>
     <row r="241">
-      <c r="F241" s="5" t="n"/>
       <c r="G241" s="5" t="n"/>
       <c r="H241" s="5" t="n"/>
+      <c r="I241" s="5" t="n"/>
     </row>
     <row r="242">
-      <c r="F242" s="5" t="n"/>
       <c r="G242" s="5" t="n"/>
       <c r="H242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
     </row>
     <row r="243">
-      <c r="F243" s="5" t="n"/>
       <c r="G243" s="5" t="n"/>
       <c r="H243" s="5" t="n"/>
+      <c r="I243" s="5" t="n"/>
     </row>
     <row r="244">
-      <c r="F244" s="5" t="n"/>
       <c r="G244" s="5" t="n"/>
       <c r="H244" s="5" t="n"/>
+      <c r="I244" s="5" t="n"/>
     </row>
     <row r="245">
-      <c r="F245" s="5" t="n"/>
       <c r="G245" s="5" t="n"/>
       <c r="H245" s="5" t="n"/>
+      <c r="I245" s="5" t="n"/>
     </row>
     <row r="246">
-      <c r="F246" s="5" t="n"/>
       <c r="G246" s="5" t="n"/>
       <c r="H246" s="5" t="n"/>
+      <c r="I246" s="5" t="n"/>
     </row>
     <row r="247">
-      <c r="F247" s="5" t="n"/>
       <c r="G247" s="5" t="n"/>
       <c r="H247" s="5" t="n"/>
+      <c r="I247" s="5" t="n"/>
     </row>
     <row r="248">
-      <c r="F248" s="5" t="n"/>
       <c r="G248" s="5" t="n"/>
       <c r="H248" s="5" t="n"/>
+      <c r="I248" s="5" t="n"/>
     </row>
     <row r="249">
-      <c r="F249" s="5" t="n"/>
       <c r="G249" s="5" t="n"/>
       <c r="H249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
     </row>
     <row r="250">
-      <c r="F250" s="5" t="n"/>
       <c r="G250" s="5" t="n"/>
       <c r="H250" s="5" t="n"/>
+      <c r="I250" s="5" t="n"/>
     </row>
     <row r="251">
-      <c r="F251" s="5" t="n"/>
       <c r="G251" s="5" t="n"/>
       <c r="H251" s="5" t="n"/>
+      <c r="I251" s="5" t="n"/>
     </row>
     <row r="252">
-      <c r="F252" s="5" t="n"/>
       <c r="G252" s="5" t="n"/>
       <c r="H252" s="5" t="n"/>
+      <c r="I252" s="5" t="n"/>
     </row>
     <row r="253">
-      <c r="F253" s="5" t="n"/>
       <c r="G253" s="5" t="n"/>
       <c r="H253" s="5" t="n"/>
+      <c r="I253" s="5" t="n"/>
     </row>
     <row r="254">
-      <c r="F254" s="5" t="n"/>
       <c r="G254" s="5" t="n"/>
       <c r="H254" s="5" t="n"/>
+      <c r="I254" s="5" t="n"/>
     </row>
     <row r="255">
-      <c r="F255" s="5" t="n"/>
       <c r="G255" s="5" t="n"/>
       <c r="H255" s="5" t="n"/>
+      <c r="I255" s="5" t="n"/>
     </row>
     <row r="256">
-      <c r="F256" s="5" t="n"/>
       <c r="G256" s="5" t="n"/>
       <c r="H256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
     </row>
     <row r="257">
-      <c r="F257" s="5" t="n"/>
       <c r="G257" s="5" t="n"/>
       <c r="H257" s="5" t="n"/>
+      <c r="I257" s="5" t="n"/>
     </row>
     <row r="258">
-      <c r="F258" s="5" t="n"/>
       <c r="G258" s="5" t="n"/>
       <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
     </row>
     <row r="259">
-      <c r="F259" s="5" t="n"/>
       <c r="G259" s="5" t="n"/>
       <c r="H259" s="5" t="n"/>
+      <c r="I259" s="5" t="n"/>
     </row>
     <row r="260">
-      <c r="F260" s="5" t="n"/>
       <c r="G260" s="5" t="n"/>
       <c r="H260" s="5" t="n"/>
+      <c r="I260" s="5" t="n"/>
     </row>
     <row r="261">
-      <c r="F261" s="5" t="n"/>
       <c r="G261" s="5" t="n"/>
       <c r="H261" s="5" t="n"/>
+      <c r="I261" s="5" t="n"/>
     </row>
     <row r="262">
-      <c r="F262" s="5" t="n"/>
       <c r="G262" s="5" t="n"/>
       <c r="H262" s="5" t="n"/>
+      <c r="I262" s="5" t="n"/>
     </row>
     <row r="263">
-      <c r="F263" s="5" t="n"/>
       <c r="G263" s="5" t="n"/>
       <c r="H263" s="5" t="n"/>
+      <c r="I263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="F264" s="5" t="n"/>
       <c r="G264" s="5" t="n"/>
       <c r="H264" s="5" t="n"/>
+      <c r="I264" s="5" t="n"/>
     </row>
     <row r="265">
-      <c r="F265" s="5" t="n"/>
       <c r="G265" s="5" t="n"/>
       <c r="H265" s="5" t="n"/>
+      <c r="I265" s="5" t="n"/>
     </row>
     <row r="266">
-      <c r="F266" s="5" t="n"/>
       <c r="G266" s="5" t="n"/>
       <c r="H266" s="5" t="n"/>
+      <c r="I266" s="5" t="n"/>
     </row>
     <row r="267">
-      <c r="F267" s="5" t="n"/>
       <c r="G267" s="5" t="n"/>
       <c r="H267" s="5" t="n"/>
+      <c r="I267" s="5" t="n"/>
     </row>
     <row r="268">
-      <c r="F268" s="5" t="n"/>
       <c r="G268" s="5" t="n"/>
       <c r="H268" s="5" t="n"/>
+      <c r="I268" s="5" t="n"/>
     </row>
     <row r="269">
-      <c r="F269" s="5" t="n"/>
       <c r="G269" s="5" t="n"/>
       <c r="H269" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
     </row>
     <row r="270">
-      <c r="F270" s="5" t="n"/>
       <c r="G270" s="5" t="n"/>
       <c r="H270" s="5" t="n"/>
+      <c r="I270" s="5" t="n"/>
     </row>
     <row r="271">
-      <c r="F271" s="5" t="n"/>
       <c r="G271" s="5" t="n"/>
       <c r="H271" s="5" t="n"/>
+      <c r="I271" s="5" t="n"/>
     </row>
     <row r="272">
-      <c r="F272" s="5" t="n"/>
       <c r="G272" s="5" t="n"/>
       <c r="H272" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
     </row>
     <row r="273">
-      <c r="F273" s="5" t="n"/>
       <c r="G273" s="5" t="n"/>
       <c r="H273" s="5" t="n"/>
+      <c r="I273" s="5" t="n"/>
     </row>
     <row r="274">
-      <c r="F274" s="5" t="n"/>
       <c r="G274" s="5" t="n"/>
       <c r="H274" s="5" t="n"/>
+      <c r="I274" s="5" t="n"/>
     </row>
     <row r="275">
-      <c r="F275" s="5" t="n"/>
       <c r="G275" s="5" t="n"/>
       <c r="H275" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
     </row>
     <row r="276">
-      <c r="F276" s="5" t="n"/>
       <c r="G276" s="5" t="n"/>
       <c r="H276" s="5" t="n"/>
+      <c r="I276" s="5" t="n"/>
     </row>
     <row r="277">
-      <c r="F277" s="5" t="n"/>
       <c r="G277" s="5" t="n"/>
       <c r="H277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
     </row>
     <row r="278">
-      <c r="F278" s="5" t="n"/>
       <c r="G278" s="5" t="n"/>
       <c r="H278" s="5" t="n"/>
+      <c r="I278" s="5" t="n"/>
     </row>
     <row r="279">
-      <c r="F279" s="5" t="n"/>
       <c r="G279" s="5" t="n"/>
       <c r="H279" s="5" t="n"/>
+      <c r="I279" s="5" t="n"/>
     </row>
     <row r="280">
-      <c r="F280" s="5" t="n"/>
       <c r="G280" s="5" t="n"/>
       <c r="H280" s="5" t="n"/>
+      <c r="I280" s="5" t="n"/>
     </row>
     <row r="281">
-      <c r="F281" s="5" t="n"/>
       <c r="G281" s="5" t="n"/>
       <c r="H281" s="5" t="n"/>
+      <c r="I281" s="5" t="n"/>
     </row>
     <row r="282">
-      <c r="F282" s="5" t="n"/>
       <c r="G282" s="5" t="n"/>
       <c r="H282" s="5" t="n"/>
+      <c r="I282" s="5" t="n"/>
     </row>
     <row r="283">
-      <c r="F283" s="5" t="n"/>
       <c r="G283" s="5" t="n"/>
       <c r="H283" s="5" t="n"/>
+      <c r="I283" s="5" t="n"/>
     </row>
     <row r="284">
-      <c r="F284" s="5" t="n"/>
       <c r="G284" s="5" t="n"/>
       <c r="H284" s="5" t="n"/>
+      <c r="I284" s="5" t="n"/>
     </row>
     <row r="285">
-      <c r="F285" s="5" t="n"/>
       <c r="G285" s="5" t="n"/>
       <c r="H285" s="5" t="n"/>
+      <c r="I285" s="5" t="n"/>
     </row>
     <row r="286">
-      <c r="F286" s="5" t="n"/>
       <c r="G286" s="5" t="n"/>
       <c r="H286" s="5" t="n"/>
+      <c r="I286" s="5" t="n"/>
     </row>
     <row r="287">
-      <c r="F287" s="5" t="n"/>
       <c r="G287" s="5" t="n"/>
       <c r="H287" s="5" t="n"/>
+      <c r="I287" s="5" t="n"/>
     </row>
     <row r="288">
-      <c r="F288" s="5" t="n"/>
       <c r="G288" s="5" t="n"/>
       <c r="H288" s="5" t="n"/>
+      <c r="I288" s="5" t="n"/>
     </row>
     <row r="289">
-      <c r="F289" s="5" t="n"/>
       <c r="G289" s="5" t="n"/>
       <c r="H289" s="5" t="n"/>
+      <c r="I289" s="5" t="n"/>
     </row>
     <row r="290">
-      <c r="F290" s="5" t="n"/>
       <c r="G290" s="5" t="n"/>
       <c r="H290" s="5" t="n"/>
+      <c r="I290" s="5" t="n"/>
     </row>
     <row r="291">
-      <c r="F291" s="5" t="n"/>
       <c r="G291" s="5" t="n"/>
       <c r="H291" s="5" t="n"/>
+      <c r="I291" s="5" t="n"/>
     </row>
     <row r="292">
-      <c r="F292" s="5" t="n"/>
       <c r="G292" s="5" t="n"/>
       <c r="H292" s="5" t="n"/>
+      <c r="I292" s="5" t="n"/>
     </row>
     <row r="293">
-      <c r="F293" s="5" t="n"/>
       <c r="G293" s="5" t="n"/>
       <c r="H293" s="5" t="n"/>
+      <c r="I293" s="5" t="n"/>
     </row>
     <row r="294">
-      <c r="F294" s="5" t="n"/>
       <c r="G294" s="5" t="n"/>
       <c r="H294" s="5" t="n"/>
+      <c r="I294" s="5" t="n"/>
     </row>
     <row r="295">
-      <c r="F295" s="5" t="n"/>
       <c r="G295" s="5" t="n"/>
       <c r="H295" s="5" t="n"/>
+      <c r="I295" s="5" t="n"/>
     </row>
     <row r="296">
-      <c r="F296" s="5" t="n"/>
       <c r="G296" s="5" t="n"/>
       <c r="H296" s="5" t="n"/>
+      <c r="I296" s="5" t="n"/>
     </row>
     <row r="297">
-      <c r="F297" s="5" t="n"/>
       <c r="G297" s="5" t="n"/>
       <c r="H297" s="5" t="n"/>
+      <c r="I297" s="5" t="n"/>
     </row>
     <row r="298">
-      <c r="F298" s="5" t="n"/>
       <c r="G298" s="5" t="n"/>
       <c r="H298" s="5" t="n"/>
+      <c r="I298" s="5" t="n"/>
     </row>
     <row r="299">
-      <c r="F299" s="5" t="n"/>
       <c r="G299" s="5" t="n"/>
       <c r="H299" s="5" t="n"/>
+      <c r="I299" s="5" t="n"/>
     </row>
     <row r="300">
-      <c r="F300" s="5" t="n"/>
       <c r="G300" s="5" t="n"/>
       <c r="H300" s="5" t="n"/>
+      <c r="I300" s="5" t="n"/>
     </row>
     <row r="301">
-      <c r="F301" s="5" t="n"/>
       <c r="G301" s="5" t="n"/>
       <c r="H301" s="5" t="n"/>
+      <c r="I301" s="5" t="n"/>
     </row>
     <row r="302">
-      <c r="F302" s="5" t="n"/>
       <c r="G302" s="5" t="n"/>
       <c r="H302" s="5" t="n"/>
+      <c r="I302" s="5" t="n"/>
     </row>
     <row r="303">
-      <c r="F303" s="5" t="n"/>
       <c r="G303" s="5" t="n"/>
       <c r="H303" s="5" t="n"/>
+      <c r="I303" s="5" t="n"/>
     </row>
     <row r="304">
-      <c r="F304" s="5" t="n"/>
       <c r="G304" s="5" t="n"/>
       <c r="H304" s="5" t="n"/>
+      <c r="I304" s="5" t="n"/>
     </row>
     <row r="305">
-      <c r="F305" s="5" t="n"/>
       <c r="G305" s="5" t="n"/>
       <c r="H305" s="5" t="n"/>
+      <c r="I305" s="5" t="n"/>
     </row>
     <row r="306">
-      <c r="F306" s="5" t="n"/>
       <c r="G306" s="5" t="n"/>
       <c r="H306" s="5" t="n"/>
+      <c r="I306" s="5" t="n"/>
     </row>
     <row r="307">
-      <c r="F307" s="5" t="n"/>
       <c r="G307" s="5" t="n"/>
       <c r="H307" s="5" t="n"/>
+      <c r="I307" s="5" t="n"/>
     </row>
     <row r="308">
-      <c r="F308" s="5" t="n"/>
       <c r="G308" s="5" t="n"/>
       <c r="H308" s="5" t="n"/>
+      <c r="I308" s="5" t="n"/>
     </row>
     <row r="309">
-      <c r="F309" s="5" t="n"/>
       <c r="G309" s="5" t="n"/>
       <c r="H309" s="5" t="n"/>
+      <c r="I309" s="5" t="n"/>
     </row>
     <row r="310">
-      <c r="F310" s="5" t="n"/>
       <c r="G310" s="5" t="n"/>
       <c r="H310" s="5" t="n"/>
+      <c r="I310" s="5" t="n"/>
     </row>
     <row r="311">
-      <c r="F311" s="5" t="n"/>
       <c r="G311" s="5" t="n"/>
       <c r="H311" s="5" t="n"/>
+      <c r="I311" s="5" t="n"/>
     </row>
     <row r="312">
-      <c r="F312" s="5" t="n"/>
       <c r="G312" s="5" t="n"/>
       <c r="H312" s="5" t="n"/>
+      <c r="I312" s="5" t="n"/>
     </row>
     <row r="313">
-      <c r="F313" s="5" t="n"/>
       <c r="G313" s="5" t="n"/>
       <c r="H313" s="5" t="n"/>
+      <c r="I313" s="5" t="n"/>
     </row>
     <row r="314">
-      <c r="F314" s="5" t="n"/>
       <c r="G314" s="5" t="n"/>
       <c r="H314" s="5" t="n"/>
+      <c r="I314" s="5" t="n"/>
     </row>
     <row r="315">
-      <c r="F315" s="5" t="n"/>
       <c r="G315" s="5" t="n"/>
       <c r="H315" s="5" t="n"/>
+      <c r="I315" s="5" t="n"/>
     </row>
     <row r="316">
-      <c r="F316" s="5" t="n"/>
       <c r="G316" s="5" t="n"/>
       <c r="H316" s="5" t="n"/>
+      <c r="I316" s="5" t="n"/>
     </row>
     <row r="317">
-      <c r="F317" s="5" t="n"/>
       <c r="G317" s="5" t="n"/>
       <c r="H317" s="5" t="n"/>
+      <c r="I317" s="5" t="n"/>
     </row>
     <row r="318">
-      <c r="F318" s="5" t="n"/>
       <c r="G318" s="5" t="n"/>
       <c r="H318" s="5" t="n"/>
+      <c r="I318" s="5" t="n"/>
     </row>
     <row r="319">
-      <c r="F319" s="5" t="n"/>
       <c r="G319" s="5" t="n"/>
       <c r="H319" s="5" t="n"/>
+      <c r="I319" s="5" t="n"/>
     </row>
     <row r="320">
-      <c r="F320" s="5" t="n"/>
       <c r="G320" s="5" t="n"/>
       <c r="H320" s="5" t="n"/>
+      <c r="I320" s="5" t="n"/>
     </row>
     <row r="321">
-      <c r="F321" s="5" t="n"/>
       <c r="G321" s="5" t="n"/>
       <c r="H321" s="5" t="n"/>
+      <c r="I321" s="5" t="n"/>
     </row>
     <row r="322">
-      <c r="F322" s="5" t="n"/>
       <c r="G322" s="5" t="n"/>
       <c r="H322" s="5" t="n"/>
+      <c r="I322" s="5" t="n"/>
     </row>
     <row r="323">
-      <c r="F323" s="5" t="n"/>
       <c r="G323" s="5" t="n"/>
       <c r="H323" s="5" t="n"/>
+      <c r="I323" s="5" t="n"/>
     </row>
     <row r="324">
-      <c r="F324" s="5" t="n"/>
       <c r="G324" s="5" t="n"/>
       <c r="H324" s="5" t="n"/>
+      <c r="I324" s="5" t="n"/>
     </row>
     <row r="325">
-      <c r="F325" s="5" t="n"/>
       <c r="G325" s="5" t="n"/>
       <c r="H325" s="5" t="n"/>
+      <c r="I325" s="5" t="n"/>
     </row>
     <row r="326">
-      <c r="F326" s="5" t="n"/>
       <c r="G326" s="5" t="n"/>
       <c r="H326" s="5" t="n"/>
+      <c r="I326" s="5" t="n"/>
     </row>
     <row r="327">
-      <c r="F327" s="5" t="n"/>
       <c r="G327" s="5" t="n"/>
       <c r="H327" s="5" t="n"/>
+      <c r="I327" s="5" t="n"/>
     </row>
     <row r="328">
-      <c r="F328" s="5" t="n"/>
       <c r="G328" s="5" t="n"/>
       <c r="H328" s="5" t="n"/>
+      <c r="I328" s="5" t="n"/>
     </row>
     <row r="329">
-      <c r="F329" s="5" t="n"/>
       <c r="G329" s="5" t="n"/>
       <c r="H329" s="5" t="n"/>
+      <c r="I329" s="5" t="n"/>
     </row>
     <row r="330">
-      <c r="F330" s="5" t="n"/>
       <c r="G330" s="5" t="n"/>
       <c r="H330" s="5" t="n"/>
+      <c r="I330" s="5" t="n"/>
     </row>
     <row r="331">
-      <c r="F331" s="5" t="n"/>
       <c r="G331" s="5" t="n"/>
       <c r="H331" s="5" t="n"/>
+      <c r="I331" s="5" t="n"/>
     </row>
     <row r="332">
-      <c r="F332" s="5" t="n"/>
       <c r="G332" s="5" t="n"/>
       <c r="H332" s="5" t="n"/>
+      <c r="I332" s="5" t="n"/>
     </row>
     <row r="333">
-      <c r="F333" s="5" t="n"/>
       <c r="G333" s="5" t="n"/>
       <c r="H333" s="5" t="n"/>
+      <c r="I333" s="5" t="n"/>
     </row>
     <row r="334">
-      <c r="F334" s="5" t="n"/>
       <c r="G334" s="5" t="n"/>
       <c r="H334" s="5" t="n"/>
+      <c r="I334" s="5" t="n"/>
     </row>
     <row r="335">
-      <c r="F335" s="5" t="n"/>
       <c r="G335" s="5" t="n"/>
       <c r="H335" s="5" t="n"/>
+      <c r="I335" s="5" t="n"/>
     </row>
     <row r="336">
-      <c r="F336" s="5" t="n"/>
       <c r="G336" s="5" t="n"/>
       <c r="H336" s="5" t="n"/>
+      <c r="I336" s="5" t="n"/>
     </row>
     <row r="337">
-      <c r="F337" s="5" t="n"/>
       <c r="G337" s="5" t="n"/>
       <c r="H337" s="5" t="n"/>
+      <c r="I337" s="5" t="n"/>
     </row>
     <row r="338">
-      <c r="F338" s="5" t="n"/>
       <c r="G338" s="5" t="n"/>
       <c r="H338" s="5" t="n"/>
+      <c r="I338" s="5" t="n"/>
     </row>
     <row r="339">
-      <c r="F339" s="5" t="n"/>
       <c r="G339" s="5" t="n"/>
       <c r="H339" s="5" t="n"/>
+      <c r="I339" s="5" t="n"/>
     </row>
     <row r="340">
-      <c r="F340" s="5" t="n"/>
       <c r="G340" s="5" t="n"/>
       <c r="H340" s="5" t="n"/>
+      <c r="I340" s="5" t="n"/>
     </row>
     <row r="341">
-      <c r="F341" s="5" t="n"/>
       <c r="G341" s="5" t="n"/>
       <c r="H341" s="5" t="n"/>
+      <c r="I341" s="5" t="n"/>
     </row>
     <row r="342">
-      <c r="F342" s="5" t="n"/>
       <c r="G342" s="5" t="n"/>
       <c r="H342" s="5" t="n"/>
+      <c r="I342" s="5" t="n"/>
     </row>
     <row r="343">
-      <c r="F343" s="5" t="n"/>
       <c r="G343" s="5" t="n"/>
       <c r="H343" s="5" t="n"/>
+      <c r="I343" s="5" t="n"/>
     </row>
     <row r="344">
-      <c r="F344" s="5" t="n"/>
       <c r="G344" s="5" t="n"/>
       <c r="H344" s="5" t="n"/>
+      <c r="I344" s="5" t="n"/>
     </row>
     <row r="345">
-      <c r="F345" s="5" t="n"/>
       <c r="G345" s="5" t="n"/>
       <c r="H345" s="5" t="n"/>
+      <c r="I345" s="5" t="n"/>
     </row>
     <row r="346">
-      <c r="F346" s="5" t="n"/>
       <c r="G346" s="5" t="n"/>
       <c r="H346" s="5" t="n"/>
+      <c r="I346" s="5" t="n"/>
     </row>
     <row r="347">
-      <c r="F347" s="5" t="n"/>
       <c r="G347" s="5" t="n"/>
       <c r="H347" s="5" t="n"/>
+      <c r="I347" s="5" t="n"/>
     </row>
     <row r="348">
-      <c r="F348" s="5" t="n"/>
       <c r="G348" s="5" t="n"/>
       <c r="H348" s="5" t="n"/>
+      <c r="I348" s="5" t="n"/>
     </row>
     <row r="349">
-      <c r="F349" s="5" t="n"/>
       <c r="G349" s="5" t="n"/>
       <c r="H349" s="5" t="n"/>
+      <c r="I349" s="5" t="n"/>
     </row>
     <row r="350">
-      <c r="F350" s="5" t="n"/>
       <c r="G350" s="5" t="n"/>
       <c r="H350" s="5" t="n"/>
+      <c r="I350" s="5" t="n"/>
     </row>
     <row r="351">
-      <c r="F351" s="5" t="n"/>
       <c r="G351" s="5" t="n"/>
       <c r="H351" s="5" t="n"/>
+      <c r="I351" s="5" t="n"/>
     </row>
     <row r="352">
-      <c r="F352" s="5" t="n"/>
       <c r="G352" s="5" t="n"/>
       <c r="H352" s="5" t="n"/>
+      <c r="I352" s="5" t="n"/>
     </row>
     <row r="353">
-      <c r="F353" s="5" t="n"/>
       <c r="G353" s="5" t="n"/>
       <c r="H353" s="5" t="n"/>
+      <c r="I353" s="5" t="n"/>
     </row>
     <row r="354">
-      <c r="F354" s="5" t="n"/>
       <c r="G354" s="5" t="n"/>
       <c r="H354" s="5" t="n"/>
+      <c r="I354" s="5" t="n"/>
     </row>
     <row r="355">
-      <c r="F355" s="5" t="n"/>
       <c r="G355" s="5" t="n"/>
       <c r="H355" s="5" t="n"/>
+      <c r="I355" s="5" t="n"/>
     </row>
     <row r="356">
-      <c r="F356" s="5" t="n"/>
       <c r="G356" s="5" t="n"/>
       <c r="H356" s="5" t="n"/>
+      <c r="I356" s="5" t="n"/>
     </row>
     <row r="357">
-      <c r="F357" s="5" t="n"/>
       <c r="G357" s="5" t="n"/>
       <c r="H357" s="5" t="n"/>
+      <c r="I357" s="5" t="n"/>
     </row>
     <row r="358">
-      <c r="F358" s="5" t="n"/>
       <c r="G358" s="5" t="n"/>
       <c r="H358" s="5" t="n"/>
+      <c r="I358" s="5" t="n"/>
     </row>
     <row r="359">
-      <c r="F359" s="5" t="n"/>
       <c r="G359" s="5" t="n"/>
       <c r="H359" s="5" t="n"/>
+      <c r="I359" s="5" t="n"/>
     </row>
     <row r="360">
-      <c r="F360" s="5" t="n"/>
       <c r="G360" s="5" t="n"/>
       <c r="H360" s="5" t="n"/>
+      <c r="I360" s="5" t="n"/>
     </row>
     <row r="361">
-      <c r="F361" s="5" t="n"/>
       <c r="G361" s="5" t="n"/>
       <c r="H361" s="5" t="n"/>
+      <c r="I361" s="5" t="n"/>
     </row>
     <row r="362">
-      <c r="F362" s="5" t="n"/>
       <c r="G362" s="5" t="n"/>
       <c r="H362" s="5" t="n"/>
+      <c r="I362" s="5" t="n"/>
     </row>
     <row r="363">
-      <c r="F363" s="5" t="n"/>
       <c r="G363" s="5" t="n"/>
       <c r="H363" s="5" t="n"/>
+      <c r="I363" s="5" t="n"/>
     </row>
     <row r="364">
-      <c r="F364" s="5" t="n"/>
       <c r="G364" s="5" t="n"/>
       <c r="H364" s="5" t="n"/>
+      <c r="I364" s="5" t="n"/>
     </row>
     <row r="365">
-      <c r="F365" s="5" t="n"/>
       <c r="G365" s="5" t="n"/>
       <c r="H365" s="5" t="n"/>
+      <c r="I365" s="5" t="n"/>
     </row>
     <row r="366">
-      <c r="F366" s="5" t="n"/>
       <c r="G366" s="5" t="n"/>
       <c r="H366" s="5" t="n"/>
+      <c r="I366" s="5" t="n"/>
     </row>
     <row r="367">
-      <c r="F367" s="5" t="n"/>
       <c r="G367" s="5" t="n"/>
       <c r="H367" s="5" t="n"/>
+      <c r="I367" s="5" t="n"/>
     </row>
     <row r="368">
-      <c r="F368" s="5" t="n"/>
       <c r="G368" s="5" t="n"/>
       <c r="H368" s="5" t="n"/>
+      <c r="I368" s="5" t="n"/>
     </row>
     <row r="369">
-      <c r="F369" s="5" t="n"/>
       <c r="G369" s="5" t="n"/>
       <c r="H369" s="5" t="n"/>
+      <c r="I369" s="5" t="n"/>
     </row>
     <row r="370">
-      <c r="F370" s="5" t="n"/>
       <c r="G370" s="5" t="n"/>
       <c r="H370" s="5" t="n"/>
+      <c r="I370" s="5" t="n"/>
     </row>
     <row r="371">
-      <c r="F371" s="5" t="n"/>
       <c r="G371" s="5" t="n"/>
       <c r="H371" s="5" t="n"/>
+      <c r="I371" s="5" t="n"/>
     </row>
     <row r="372">
-      <c r="F372" s="5" t="n"/>
       <c r="G372" s="5" t="n"/>
       <c r="H372" s="5" t="n"/>
+      <c r="I372" s="5" t="n"/>
     </row>
     <row r="373">
-      <c r="F373" s="5" t="n"/>
       <c r="G373" s="5" t="n"/>
       <c r="H373" s="5" t="n"/>
+      <c r="I373" s="5" t="n"/>
     </row>
     <row r="374">
-      <c r="F374" s="5" t="n"/>
       <c r="G374" s="5" t="n"/>
       <c r="H374" s="5" t="n"/>
+      <c r="I374" s="5" t="n"/>
     </row>
     <row r="375">
-      <c r="F375" s="5" t="n"/>
       <c r="G375" s="5" t="n"/>
       <c r="H375" s="5" t="n"/>
+      <c r="I375" s="5" t="n"/>
     </row>
     <row r="376">
-      <c r="F376" s="5" t="n"/>
       <c r="G376" s="5" t="n"/>
       <c r="H376" s="5" t="n"/>
+      <c r="I376" s="5" t="n"/>
     </row>
     <row r="377">
-      <c r="F377" s="5" t="n"/>
       <c r="G377" s="5" t="n"/>
       <c r="H377" s="5" t="n"/>
+      <c r="I377" s="5" t="n"/>
     </row>
     <row r="378">
-      <c r="F378" s="5" t="n"/>
       <c r="G378" s="5" t="n"/>
       <c r="H378" s="5" t="n"/>
+      <c r="I378" s="5" t="n"/>
     </row>
     <row r="379">
-      <c r="F379" s="5" t="n"/>
       <c r="G379" s="5" t="n"/>
       <c r="H379" s="5" t="n"/>
+      <c r="I379" s="5" t="n"/>
     </row>
     <row r="380">
-      <c r="F380" s="5" t="n"/>
       <c r="G380" s="5" t="n"/>
       <c r="H380" s="5" t="n"/>
+      <c r="I380" s="5" t="n"/>
     </row>
     <row r="381">
-      <c r="F381" s="5" t="n"/>
       <c r="G381" s="5" t="n"/>
       <c r="H381" s="5" t="n"/>
+      <c r="I381" s="5" t="n"/>
     </row>
     <row r="382">
-      <c r="F382" s="5" t="n"/>
       <c r="G382" s="5" t="n"/>
       <c r="H382" s="5" t="n"/>
+      <c r="I382" s="5" t="n"/>
     </row>
     <row r="383">
-      <c r="F383" s="5" t="n"/>
       <c r="G383" s="5" t="n"/>
       <c r="H383" s="5" t="n"/>
+      <c r="I383" s="5" t="n"/>
     </row>
     <row r="384">
-      <c r="F384" s="5" t="n"/>
       <c r="G384" s="5" t="n"/>
       <c r="H384" s="5" t="n"/>
+      <c r="I384" s="5" t="n"/>
     </row>
     <row r="385">
-      <c r="F385" s="5" t="n"/>
       <c r="G385" s="5" t="n"/>
       <c r="H385" s="5" t="n"/>
+      <c r="I385" s="5" t="n"/>
     </row>
     <row r="386">
-      <c r="F386" s="5" t="n"/>
       <c r="G386" s="5" t="n"/>
       <c r="H386" s="5" t="n"/>
+      <c r="I386" s="5" t="n"/>
     </row>
     <row r="387">
-      <c r="F387" s="5" t="n"/>
       <c r="G387" s="5" t="n"/>
       <c r="H387" s="5" t="n"/>
+      <c r="I387" s="5" t="n"/>
     </row>
     <row r="388">
-      <c r="F388" s="5" t="n"/>
       <c r="G388" s="5" t="n"/>
       <c r="H388" s="5" t="n"/>
+      <c r="I388" s="5" t="n"/>
     </row>
     <row r="389">
-      <c r="F389" s="5" t="n"/>
       <c r="G389" s="5" t="n"/>
       <c r="H389" s="5" t="n"/>
+      <c r="I389" s="5" t="n"/>
     </row>
     <row r="390">
-      <c r="F390" s="5" t="n"/>
       <c r="G390" s="5" t="n"/>
       <c r="H390" s="5" t="n"/>
+      <c r="I390" s="5" t="n"/>
     </row>
     <row r="391">
-      <c r="F391" s="5" t="n"/>
       <c r="G391" s="5" t="n"/>
       <c r="H391" s="5" t="n"/>
+      <c r="I391" s="5" t="n"/>
     </row>
     <row r="392">
-      <c r="F392" s="5" t="n"/>
       <c r="G392" s="5" t="n"/>
       <c r="H392" s="5" t="n"/>
+      <c r="I392" s="5" t="n"/>
     </row>
     <row r="393">
-      <c r="F393" s="5" t="n"/>
       <c r="G393" s="5" t="n"/>
       <c r="H393" s="5" t="n"/>
+      <c r="I393" s="5" t="n"/>
     </row>
     <row r="394">
-      <c r="F394" s="5" t="n"/>
       <c r="G394" s="5" t="n"/>
       <c r="H394" s="5" t="n"/>
+      <c r="I394" s="5" t="n"/>
     </row>
     <row r="395">
-      <c r="F395" s="5" t="n"/>
       <c r="G395" s="5" t="n"/>
       <c r="H395" s="5" t="n"/>
+      <c r="I395" s="5" t="n"/>
     </row>
     <row r="396">
-      <c r="F396" s="5" t="n"/>
       <c r="G396" s="5" t="n"/>
       <c r="H396" s="5" t="n"/>
+      <c r="I396" s="5" t="n"/>
     </row>
     <row r="397">
-      <c r="F397" s="5" t="n"/>
       <c r="G397" s="5" t="n"/>
       <c r="H397" s="5" t="n"/>
+      <c r="I397" s="5" t="n"/>
     </row>
     <row r="398">
-      <c r="F398" s="5" t="n"/>
       <c r="G398" s="5" t="n"/>
       <c r="H398" s="5" t="n"/>
+      <c r="I398" s="5" t="n"/>
     </row>
     <row r="399">
-      <c r="F399" s="5" t="n"/>
       <c r="G399" s="5" t="n"/>
       <c r="H399" s="5" t="n"/>
+      <c r="I399" s="5" t="n"/>
     </row>
     <row r="400">
-      <c r="F400" s="5" t="n"/>
       <c r="G400" s="5" t="n"/>
       <c r="H400" s="5" t="n"/>
+      <c r="I400" s="5" t="n"/>
     </row>
     <row r="401">
-      <c r="F401" s="5" t="n"/>
       <c r="G401" s="5" t="n"/>
       <c r="H401" s="5" t="n"/>
+      <c r="I401" s="5" t="n"/>
     </row>
     <row r="402">
-      <c r="F402" s="5" t="n"/>
       <c r="G402" s="5" t="n"/>
       <c r="H402" s="5" t="n"/>
+      <c r="I402" s="5" t="n"/>
     </row>
     <row r="403">
-      <c r="F403" s="5" t="n"/>
       <c r="G403" s="5" t="n"/>
       <c r="H403" s="5" t="n"/>
+      <c r="I403" s="5" t="n"/>
     </row>
     <row r="404">
-      <c r="F404" s="5" t="n"/>
       <c r="G404" s="5" t="n"/>
       <c r="H404" s="5" t="n"/>
+      <c r="I404" s="5" t="n"/>
     </row>
     <row r="405">
-      <c r="F405" s="5" t="n"/>
       <c r="G405" s="5" t="n"/>
       <c r="H405" s="5" t="n"/>
+      <c r="I405" s="5" t="n"/>
     </row>
     <row r="406">
-      <c r="F406" s="5" t="n"/>
       <c r="G406" s="5" t="n"/>
       <c r="H406" s="5" t="n"/>
+      <c r="I406" s="5" t="n"/>
     </row>
     <row r="407">
-      <c r="F407" s="5" t="n"/>
       <c r="G407" s="5" t="n"/>
       <c r="H407" s="5" t="n"/>
+      <c r="I407" s="5" t="n"/>
     </row>
     <row r="408">
-      <c r="F408" s="5" t="n"/>
       <c r="G408" s="5" t="n"/>
       <c r="H408" s="5" t="n"/>
+      <c r="I408" s="5" t="n"/>
     </row>
     <row r="409">
-      <c r="F409" s="5" t="n"/>
       <c r="G409" s="5" t="n"/>
       <c r="H409" s="5" t="n"/>
+      <c r="I409" s="5" t="n"/>
     </row>
     <row r="410">
-      <c r="F410" s="5" t="n"/>
       <c r="G410" s="5" t="n"/>
       <c r="H410" s="5" t="n"/>
+      <c r="I410" s="5" t="n"/>
     </row>
     <row r="411">
-      <c r="F411" s="5" t="n"/>
       <c r="G411" s="5" t="n"/>
       <c r="H411" s="5" t="n"/>
+      <c r="I411" s="5" t="n"/>
     </row>
     <row r="412">
-      <c r="F412" s="5" t="n"/>
       <c r="G412" s="5" t="n"/>
       <c r="H412" s="5" t="n"/>
+      <c r="I412" s="5" t="n"/>
     </row>
     <row r="413">
-      <c r="F413" s="5" t="n"/>
       <c r="G413" s="5" t="n"/>
       <c r="H413" s="5" t="n"/>
+      <c r="I413" s="5" t="n"/>
     </row>
     <row r="414">
-      <c r="F414" s="5" t="n"/>
       <c r="G414" s="5" t="n"/>
       <c r="H414" s="5" t="n"/>
+      <c r="I414" s="5" t="n"/>
     </row>
     <row r="415">
-      <c r="F415" s="5" t="n"/>
       <c r="G415" s="5" t="n"/>
       <c r="H415" s="5" t="n"/>
+      <c r="I415" s="5" t="n"/>
     </row>
     <row r="416">
-      <c r="F416" s="5" t="n"/>
       <c r="G416" s="5" t="n"/>
       <c r="H416" s="5" t="n"/>
+      <c r="I416" s="5" t="n"/>
     </row>
     <row r="417">
-      <c r="F417" s="5" t="n"/>
       <c r="G417" s="5" t="n"/>
       <c r="H417" s="5" t="n"/>
+      <c r="I417" s="5" t="n"/>
     </row>
     <row r="418">
-      <c r="F418" s="5" t="n"/>
       <c r="G418" s="5" t="n"/>
       <c r="H418" s="5" t="n"/>
+      <c r="I418" s="5" t="n"/>
     </row>
     <row r="419">
-      <c r="F419" s="5" t="n"/>
       <c r="G419" s="5" t="n"/>
       <c r="H419" s="5" t="n"/>
+      <c r="I419" s="5" t="n"/>
     </row>
     <row r="420">
-      <c r="F420" s="5" t="n"/>
       <c r="G420" s="5" t="n"/>
       <c r="H420" s="5" t="n"/>
+      <c r="I420" s="5" t="n"/>
     </row>
     <row r="421">
-      <c r="F421" s="5" t="n"/>
       <c r="G421" s="5" t="n"/>
       <c r="H421" s="5" t="n"/>
+      <c r="I421" s="5" t="n"/>
     </row>
     <row r="422">
-      <c r="F422" s="5" t="n"/>
       <c r="G422" s="5" t="n"/>
       <c r="H422" s="5" t="n"/>
+      <c r="I422" s="5" t="n"/>
     </row>
     <row r="423">
-      <c r="F423" s="5" t="n"/>
       <c r="G423" s="5" t="n"/>
       <c r="H423" s="5" t="n"/>
+      <c r="I423" s="5" t="n"/>
     </row>
     <row r="424">
-      <c r="F424" s="5" t="n"/>
       <c r="G424" s="5" t="n"/>
       <c r="H424" s="5" t="n"/>
+      <c r="I424" s="5" t="n"/>
     </row>
     <row r="425">
-      <c r="F425" s="5" t="n"/>
       <c r="G425" s="5" t="n"/>
       <c r="H425" s="5" t="n"/>
+      <c r="I425" s="5" t="n"/>
     </row>
     <row r="426">
-      <c r="F426" s="5" t="n"/>
       <c r="G426" s="5" t="n"/>
       <c r="H426" s="5" t="n"/>
+      <c r="I426" s="5" t="n"/>
     </row>
     <row r="427">
-      <c r="F427" s="5" t="n"/>
       <c r="G427" s="5" t="n"/>
       <c r="H427" s="5" t="n"/>
+      <c r="I427" s="5" t="n"/>
     </row>
     <row r="428">
-      <c r="F428" s="5" t="n"/>
       <c r="G428" s="5" t="n"/>
       <c r="H428" s="5" t="n"/>
+      <c r="I428" s="5" t="n"/>
     </row>
     <row r="429">
-      <c r="F429" s="5" t="n"/>
       <c r="G429" s="5" t="n"/>
       <c r="H429" s="5" t="n"/>
+      <c r="I429" s="5" t="n"/>
     </row>
     <row r="430">
-      <c r="F430" s="5" t="n"/>
       <c r="G430" s="5" t="n"/>
       <c r="H430" s="5" t="n"/>
+      <c r="I430" s="5" t="n"/>
     </row>
     <row r="431">
-      <c r="F431" s="5" t="n"/>
       <c r="G431" s="5" t="n"/>
       <c r="H431" s="5" t="n"/>
+      <c r="I431" s="5" t="n"/>
     </row>
     <row r="432">
-      <c r="F432" s="5" t="n"/>
       <c r="G432" s="5" t="n"/>
       <c r="H432" s="5" t="n"/>
+      <c r="I432" s="5" t="n"/>
     </row>
     <row r="433">
-      <c r="F433" s="5" t="n"/>
       <c r="G433" s="5" t="n"/>
       <c r="H433" s="5" t="n"/>
+      <c r="I433" s="5" t="n"/>
     </row>
     <row r="434">
-      <c r="F434" s="5" t="n"/>
       <c r="G434" s="5" t="n"/>
       <c r="H434" s="5" t="n"/>
+      <c r="I434" s="5" t="n"/>
     </row>
     <row r="435">
-      <c r="F435" s="5" t="n"/>
       <c r="G435" s="5" t="n"/>
       <c r="H435" s="5" t="n"/>
+      <c r="I435" s="5" t="n"/>
     </row>
     <row r="436">
-      <c r="F436" s="5" t="n"/>
       <c r="G436" s="5" t="n"/>
       <c r="H436" s="5" t="n"/>
+      <c r="I436" s="5" t="n"/>
     </row>
     <row r="437">
-      <c r="F437" s="5" t="n"/>
       <c r="G437" s="5" t="n"/>
       <c r="H437" s="5" t="n"/>
+      <c r="I437" s="5" t="n"/>
     </row>
     <row r="438">
-      <c r="F438" s="5" t="n"/>
       <c r="G438" s="5" t="n"/>
       <c r="H438" s="5" t="n"/>
+      <c r="I438" s="5" t="n"/>
     </row>
     <row r="439">
-      <c r="F439" s="5" t="n"/>
       <c r="G439" s="5" t="n"/>
       <c r="H439" s="5" t="n"/>
+      <c r="I439" s="5" t="n"/>
     </row>
     <row r="440">
-      <c r="F440" s="5" t="n"/>
       <c r="G440" s="5" t="n"/>
       <c r="H440" s="5" t="n"/>
+      <c r="I440" s="5" t="n"/>
     </row>
     <row r="441">
-      <c r="F441" s="5" t="n"/>
       <c r="G441" s="5" t="n"/>
       <c r="H441" s="5" t="n"/>
+      <c r="I441" s="5" t="n"/>
     </row>
     <row r="442">
-      <c r="F442" s="5" t="n"/>
       <c r="G442" s="5" t="n"/>
       <c r="H442" s="5" t="n"/>
+      <c r="I442" s="5" t="n"/>
     </row>
     <row r="443">
-      <c r="F443" s="5" t="n"/>
       <c r="G443" s="5" t="n"/>
       <c r="H443" s="5" t="n"/>
+      <c r="I443" s="5" t="n"/>
     </row>
     <row r="444">
-      <c r="F444" s="5" t="n"/>
       <c r="G444" s="5" t="n"/>
       <c r="H444" s="5" t="n"/>
+      <c r="I444" s="5" t="n"/>
     </row>
     <row r="445">
-      <c r="F445" s="5" t="n"/>
       <c r="G445" s="5" t="n"/>
       <c r="H445" s="5" t="n"/>
+      <c r="I445" s="5" t="n"/>
     </row>
     <row r="446">
-      <c r="F446" s="5" t="n"/>
       <c r="G446" s="5" t="n"/>
       <c r="H446" s="5" t="n"/>
+      <c r="I446" s="5" t="n"/>
     </row>
     <row r="447">
-      <c r="F447" s="5" t="n"/>
       <c r="G447" s="5" t="n"/>
       <c r="H447" s="5" t="n"/>
+      <c r="I447" s="5" t="n"/>
     </row>
     <row r="448">
-      <c r="F448" s="5" t="n"/>
       <c r="G448" s="5" t="n"/>
       <c r="H448" s="5" t="n"/>
+      <c r="I448" s="5" t="n"/>
     </row>
     <row r="449">
-      <c r="F449" s="5" t="n"/>
       <c r="G449" s="5" t="n"/>
       <c r="H449" s="5" t="n"/>
+      <c r="I449" s="5" t="n"/>
     </row>
     <row r="450">
-      <c r="F450" s="5" t="n"/>
       <c r="G450" s="5" t="n"/>
       <c r="H450" s="5" t="n"/>
+      <c r="I450" s="5" t="n"/>
     </row>
     <row r="451">
-      <c r="F451" s="5" t="n"/>
       <c r="G451" s="5" t="n"/>
       <c r="H451" s="5" t="n"/>
+      <c r="I451" s="5" t="n"/>
     </row>
     <row r="452">
-      <c r="F452" s="5" t="n"/>
       <c r="G452" s="5" t="n"/>
       <c r="H452" s="5" t="n"/>
+      <c r="I452" s="5" t="n"/>
     </row>
     <row r="453">
-      <c r="F453" s="5" t="n"/>
       <c r="G453" s="5" t="n"/>
       <c r="H453" s="5" t="n"/>
+      <c r="I453" s="5" t="n"/>
     </row>
     <row r="454">
-      <c r="F454" s="5" t="n"/>
       <c r="G454" s="5" t="n"/>
       <c r="H454" s="5" t="n"/>
+      <c r="I454" s="5" t="n"/>
     </row>
     <row r="455">
-      <c r="F455" s="5" t="n"/>
       <c r="G455" s="5" t="n"/>
       <c r="H455" s="5" t="n"/>
+      <c r="I455" s="5" t="n"/>
     </row>
     <row r="456">
-      <c r="F456" s="5" t="n"/>
       <c r="G456" s="5" t="n"/>
       <c r="H456" s="5" t="n"/>
+      <c r="I456" s="5" t="n"/>
     </row>
     <row r="457">
-      <c r="F457" s="5" t="n"/>
       <c r="G457" s="5" t="n"/>
       <c r="H457" s="5" t="n"/>
+      <c r="I457" s="5" t="n"/>
     </row>
     <row r="458">
-      <c r="F458" s="5" t="n"/>
       <c r="G458" s="5" t="n"/>
       <c r="H458" s="5" t="n"/>
+      <c r="I458" s="5" t="n"/>
     </row>
     <row r="459">
-      <c r="F459" s="5" t="n"/>
       <c r="G459" s="5" t="n"/>
       <c r="H459" s="5" t="n"/>
+      <c r="I459" s="5" t="n"/>
     </row>
     <row r="460">
-      <c r="F460" s="5" t="n"/>
       <c r="G460" s="5" t="n"/>
       <c r="H460" s="5" t="n"/>
+      <c r="I460" s="5" t="n"/>
     </row>
     <row r="461">
-      <c r="F461" s="5" t="n"/>
       <c r="G461" s="5" t="n"/>
       <c r="H461" s="5" t="n"/>
+      <c r="I461" s="5" t="n"/>
     </row>
     <row r="462">
-      <c r="F462" s="5" t="n"/>
       <c r="G462" s="5" t="n"/>
       <c r="H462" s="5" t="n"/>
+      <c r="I462" s="5" t="n"/>
     </row>
     <row r="463">
-      <c r="F463" s="5" t="n"/>
       <c r="G463" s="5" t="n"/>
       <c r="H463" s="5" t="n"/>
+      <c r="I463" s="5" t="n"/>
     </row>
     <row r="464">
-      <c r="F464" s="5" t="n"/>
       <c r="G464" s="5" t="n"/>
       <c r="H464" s="5" t="n"/>
+      <c r="I464" s="5" t="n"/>
     </row>
     <row r="465">
-      <c r="F465" s="5" t="n"/>
       <c r="G465" s="5" t="n"/>
       <c r="H465" s="5" t="n"/>
+      <c r="I465" s="5" t="n"/>
     </row>
     <row r="466">
-      <c r="F466" s="5" t="n"/>
       <c r="G466" s="5" t="n"/>
       <c r="H466" s="5" t="n"/>
+      <c r="I466" s="5" t="n"/>
     </row>
     <row r="467">
-      <c r="F467" s="5" t="n"/>
       <c r="G467" s="5" t="n"/>
       <c r="H467" s="5" t="n"/>
+      <c r="I467" s="5" t="n"/>
     </row>
     <row r="468">
-      <c r="F468" s="5" t="n"/>
       <c r="G468" s="5" t="n"/>
       <c r="H468" s="5" t="n"/>
+      <c r="I468" s="5" t="n"/>
     </row>
     <row r="469">
-      <c r="F469" s="5" t="n"/>
       <c r="G469" s="5" t="n"/>
       <c r="H469" s="5" t="n"/>
+      <c r="I469" s="5" t="n"/>
     </row>
     <row r="470">
-      <c r="F470" s="5" t="n"/>
       <c r="G470" s="5" t="n"/>
       <c r="H470" s="5" t="n"/>
+      <c r="I470" s="5" t="n"/>
     </row>
     <row r="471">
-      <c r="F471" s="5" t="n"/>
       <c r="G471" s="5" t="n"/>
       <c r="H471" s="5" t="n"/>
+      <c r="I471" s="5" t="n"/>
     </row>
     <row r="472">
-      <c r="F472" s="5" t="n"/>
       <c r="G472" s="5" t="n"/>
       <c r="H472" s="5" t="n"/>
+      <c r="I472" s="5" t="n"/>
     </row>
     <row r="473">
-      <c r="F473" s="5" t="n"/>
       <c r="G473" s="5" t="n"/>
       <c r="H473" s="5" t="n"/>
+      <c r="I473" s="5" t="n"/>
     </row>
     <row r="474">
-      <c r="F474" s="5" t="n"/>
       <c r="G474" s="5" t="n"/>
       <c r="H474" s="5" t="n"/>
+      <c r="I474" s="5" t="n"/>
     </row>
     <row r="475">
-      <c r="F475" s="5" t="n"/>
       <c r="G475" s="5" t="n"/>
       <c r="H475" s="5" t="n"/>
+      <c r="I475" s="5" t="n"/>
     </row>
     <row r="476">
-      <c r="F476" s="5" t="n"/>
       <c r="G476" s="5" t="n"/>
       <c r="H476" s="5" t="n"/>
+      <c r="I476" s="5" t="n"/>
     </row>
     <row r="477">
-      <c r="F477" s="5" t="n"/>
       <c r="G477" s="5" t="n"/>
       <c r="H477" s="5" t="n"/>
+      <c r="I477" s="5" t="n"/>
     </row>
     <row r="478">
-      <c r="F478" s="5" t="n"/>
       <c r="G478" s="5" t="n"/>
       <c r="H478" s="5" t="n"/>
+      <c r="I478" s="5" t="n"/>
     </row>
     <row r="479">
-      <c r="F479" s="5" t="n"/>
       <c r="G479" s="5" t="n"/>
       <c r="H479" s="5" t="n"/>
+      <c r="I479" s="5" t="n"/>
     </row>
     <row r="480">
-      <c r="F480" s="5" t="n"/>
       <c r="G480" s="5" t="n"/>
       <c r="H480" s="5" t="n"/>
+      <c r="I480" s="5" t="n"/>
     </row>
     <row r="481">
-      <c r="F481" s="5" t="n"/>
       <c r="G481" s="5" t="n"/>
       <c r="H481" s="5" t="n"/>
+      <c r="I481" s="5" t="n"/>
     </row>
     <row r="482">
-      <c r="F482" s="5" t="n"/>
       <c r="G482" s="5" t="n"/>
       <c r="H482" s="5" t="n"/>
+      <c r="I482" s="5" t="n"/>
     </row>
     <row r="483">
-      <c r="F483" s="5" t="n"/>
       <c r="G483" s="5" t="n"/>
       <c r="H483" s="5" t="n"/>
+      <c r="I483" s="5" t="n"/>
     </row>
     <row r="484">
-      <c r="F484" s="5" t="n"/>
       <c r="G484" s="5" t="n"/>
       <c r="H484" s="5" t="n"/>
+      <c r="I484" s="5" t="n"/>
     </row>
     <row r="485">
-      <c r="F485" s="5" t="n"/>
       <c r="G485" s="5" t="n"/>
       <c r="H485" s="5" t="n"/>
+      <c r="I485" s="5" t="n"/>
     </row>
     <row r="486">
-      <c r="F486" s="5" t="n"/>
       <c r="G486" s="5" t="n"/>
       <c r="H486" s="5" t="n"/>
+      <c r="I486" s="5" t="n"/>
     </row>
     <row r="487">
-      <c r="F487" s="5" t="n"/>
       <c r="G487" s="5" t="n"/>
       <c r="H487" s="5" t="n"/>
+      <c r="I487" s="5" t="n"/>
     </row>
     <row r="488">
-      <c r="F488" s="5" t="n"/>
       <c r="G488" s="5" t="n"/>
       <c r="H488" s="5" t="n"/>
+      <c r="I488" s="5" t="n"/>
     </row>
     <row r="489">
-      <c r="F489" s="5" t="n"/>
       <c r="G489" s="5" t="n"/>
       <c r="H489" s="5" t="n"/>
+      <c r="I489" s="5" t="n"/>
     </row>
     <row r="490">
-      <c r="F490" s="5" t="n"/>
       <c r="G490" s="5" t="n"/>
       <c r="H490" s="5" t="n"/>
+      <c r="I490" s="5" t="n"/>
     </row>
     <row r="491">
-      <c r="F491" s="5" t="n"/>
       <c r="G491" s="5" t="n"/>
       <c r="H491" s="5" t="n"/>
+      <c r="I491" s="5" t="n"/>
     </row>
     <row r="492">
-      <c r="F492" s="5" t="n"/>
       <c r="G492" s="5" t="n"/>
       <c r="H492" s="5" t="n"/>
+      <c r="I492" s="5" t="n"/>
     </row>
     <row r="493">
-      <c r="F493" s="5" t="n"/>
       <c r="G493" s="5" t="n"/>
       <c r="H493" s="5" t="n"/>
+      <c r="I493" s="5" t="n"/>
     </row>
     <row r="494">
-      <c r="F494" s="5" t="n"/>
       <c r="G494" s="5" t="n"/>
       <c r="H494" s="5" t="n"/>
+      <c r="I494" s="5" t="n"/>
     </row>
     <row r="495">
-      <c r="F495" s="5" t="n"/>
       <c r="G495" s="5" t="n"/>
       <c r="H495" s="5" t="n"/>
+      <c r="I495" s="5" t="n"/>
     </row>
     <row r="496">
-      <c r="F496" s="5" t="n"/>
       <c r="G496" s="5" t="n"/>
       <c r="H496" s="5" t="n"/>
+      <c r="I496" s="5" t="n"/>
     </row>
     <row r="497">
-      <c r="F497" s="5" t="n"/>
       <c r="G497" s="5" t="n"/>
       <c r="H497" s="5" t="n"/>
+      <c r="I497" s="5" t="n"/>
     </row>
     <row r="498">
-      <c r="F498" s="5" t="n"/>
       <c r="G498" s="5" t="n"/>
       <c r="H498" s="5" t="n"/>
+      <c r="I498" s="5" t="n"/>
     </row>
     <row r="499">
-      <c r="F499" s="5" t="n"/>
       <c r="G499" s="5" t="n"/>
       <c r="H499" s="5" t="n"/>
+      <c r="I499" s="5" t="n"/>
     </row>
     <row r="500">
-      <c r="F500" s="5" t="n"/>
       <c r="G500" s="5" t="n"/>
       <c r="H500" s="5" t="n"/>
+      <c r="I500" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a recognised status" error="Use one of: draft, live, submitted, won, lost" type="list">
       <formula1>"draft,live,submitted,won,lost"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not a recognised department" error="Use one of: Tipp Consulting, Tipp Resourcing, Tipp Human Capital, Tipp Construction" type="list">
+      <formula1>"Tipp Consulting,Tipp Resourcing,Tipp Human Capital,Tipp Construction"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3217,7 +3231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3287,51 +3301,51 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Which of the four owns the bid: Tipp Consulting, Tipp Resourcing, Tipp Human Capital or Tipp Construction. Pick from the dropdown. This decides who can see it, so a bid put in the wrong one is invisible to the team that owns it. Left blank it goes to the department of whoever loads the file.</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Tipp Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
           <t>reference_number</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>The issuing authority's bid number. Worth filling in: it is how the system recognises a tender it has already seen, so this file can be re-sent without creating duplicates.</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>SCM/2026/0148</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>The organisation putting the work out.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>City of Cape Town</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>client</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -3341,19 +3355,19 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Where the work happens.</t>
+          <t>The organisation putting the work out.</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Cape Town</t>
+          <t>City of Cape Town</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -3363,19 +3377,19 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Rand value. Digits only, no R and no spaces. Leave blank if not published.</t>
+          <t>Where the work happens.</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>12500000</t>
+          <t>Cape Town</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>submission_deadline</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -3385,19 +3399,19 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>When the bid is due. See the date note below.</t>
+          <t>Rand value. Digits only, no R and no spaces. Leave blank if not published.</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>12500000</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>contract_start_date</t>
+          <t>submission_deadline</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -3407,19 +3421,19 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>When the work would start if we win it.</t>
+          <t>When the bid is due. See the date note below.</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>contract_end_date</t>
+          <t>contract_start_date</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -3429,85 +3443,85 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>When it would finish. Leave blank if open ended.</t>
+          <t>When the work would start if we win it.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>2029-12-31</t>
+          <t>2027-01-04</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>contract_end_date</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>When it would finish. Leave blank if open ended.</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>One of: draft, live, submitted, won, lost. Pick from the dropdown. Blank is read as draft.</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>seats</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>The people the tender needs. Separate each role with a pipe. Put the number first with an x, and the minimum years after an @. Both are optional: a bare role name means one person with no experience floor.</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>3 x Business Analyst @5 | Project Manager @8 | 2 x ERP Consultant</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>required_skills</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Skills named in the RFQ, separated by a pipe.</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Microsoft Dynamics 365 | SQL | Power BI</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>required_certifications</t>
+          <t>required_skills</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -3517,138 +3531,173 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Certifications named in the RFQ, separated by a pipe.</t>
+          <t>Skills named in the RFQ, separated by a pipe.</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>PMP | ITIL Foundation</t>
+          <t>Microsoft Dynamics 365 | SQL | Power BI</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
+          <t>required_certifications</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Certifications named in the RFQ, separated by a pipe.</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>PMP | ITIL Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
           <t>sectors</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Sectors the work falls under, separated by a pipe.</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Public Sector | Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>min_experience_years</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>A years figure that applies to the whole tender. Any seat with its own @ number overrides it.</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>min_experience_years</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>A years figure that applies to the whole tender. Any seat with its own @ number overrides it.</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
           <t>reference_letters_required</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>How many client reference letters the tender asks for. Put 0 if it genuinely asks for none, and leave blank if nobody has checked the RFQ yet. Those are different things.</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Three things that will cause a row to be rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="62" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Dates must read 2026-10-15</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Year, then month, then day. 15/10/2026 is rejected rather than guessed at, because whether it means 15 October or the 10th of a 15th month depends on who saved the file, and guessing wrong puts a contract in the wrong month where nobody notices until it needs extending.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Role names have to match the ones the system knows</t>
+          <t>Dates must read 2026-10-15</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Write 'Business Analyst', not 'BA' or 'Snr BA'. The system scores a candidate against the exact role on the seat, so an abbreviation it does not recognise scores zero and the tender reports that nobody can fill the seat, even when three people obviously can. Common short forms like BA and PM are expanded automatically, and anything else is reported back to you in a list rather than quietly accepted.</t>
+          <t>Year, then month, then day. 15/10/2026 is rejected rather than guessed at, because whether it means 15 October or the 10th of a 15th month depends on who saved the file, and guessing wrong puts a contract in the wrong month where nobody notices until it needs extending.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
+          <t>Role names have to match the ones the system knows</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Write 'Business Analyst', not 'BA' or 'Snr BA'. The system scores a candidate against the exact role on the seat, so an abbreviation it does not recognise scores zero and the tender reports that nobody can fill the seat, even when three people obviously can. Common short forms like BA and PM are expanded automatically, and anything else is reported back to you in a list rather than quietly accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>A bid can only be seen by its own department</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Each of the four departments sees only its own tenders, so the department column decides who this bid is visible to. Getting it wrong does not produce an error: the bid is created and simply never appears for the people working on it. If a whole file belongs to one department, the column can be left blank and it will follow whoever loads it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
           <t>Use a pipe between list items</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Skills, certifications, sectors and seats all separate with a pipe. Commas are fine inside an item, so 'Roads, bridges and structures' stays as one thing.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>When it is filled in: save as CSV (File, Save As, CSV UTF-8) and send that. It is read with  npx tsx scripts/import-tenders.ts &lt;file.csv&gt;  which prints back exactly what it would do and writes nothing. Only a second run with --apply writes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C23:D23"/>
   </mergeCells>
